--- a/교재/03_차트.xlsx
+++ b/교재/03_차트.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\najon\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B032AC30-5A9F-4673-84C1-3D4B00C90351}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B483AD1-44DE-4E5B-A6FE-978EACCE4F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="차트-1" sheetId="6" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="93">
   <si>
     <t>(단위:천명, %)</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -943,6 +943,10 @@
     <t>차트 제목 수식에 = 쓰고 b1셀 클릭후 엔터</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>우클릭-&gt;축서식</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -3384,6 +3388,575 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
+              <c:f>'차트-3'!$C$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>판매가</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>('차트-3'!$B$4:$B$5,'차트-3'!$B$7:$B$8,'차트-3'!$B$11)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>노트</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>연필</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>잉크</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>파일</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>수정액</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>('차트-3'!$C$4:$C$5,'차트-3'!$C$7:$C$8,'차트-3'!$C$11)</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_ </c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>500</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-B9C1-4E6F-8DCF-4F682B3B3FC1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'차트-3'!$E$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>판매량</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>('차트-3'!$B$4:$B$5,'차트-3'!$B$7:$B$8,'차트-3'!$B$11)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>노트</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>연필</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>잉크</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>파일</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>수정액</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>('차트-3'!$E$4:$E$5,'차트-3'!$E$7:$E$8,'차트-3'!$E$11)</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0_);[Red]\(#,##0\)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1800</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>800</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1500</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>2000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>520</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-B9C1-4E6F-8DCF-4F682B3B3FC1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="100"/>
+        <c:overlap val="50"/>
+        <c:axId val="2018144127"/>
+        <c:axId val="2018139967"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredBarSeries>
+              <c15:ser>
+                <c:idx val="1"/>
+                <c:order val="1"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'차트-3'!$D$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>목표량</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:spPr>
+                  <a:solidFill>
+                    <a:schemeClr val="accent2"/>
+                  </a:solidFill>
+                  <a:ln>
+                    <a:noFill/>
+                  </a:ln>
+                  <a:effectLst/>
+                </c:spPr>
+                <c:invertIfNegative val="0"/>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>('차트-3'!$B$4:$B$5,'차트-3'!$B$7:$B$8,'차트-3'!$B$11)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>노트</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>연필</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>잉크</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>파일</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>수정액</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>('차트-3'!$D$4:$D$5,'차트-3'!$D$7:$D$8,'차트-3'!$D$11)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>#,##0_);[Red]\(#,##0\)</c:formatCode>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>1500</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>1000</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>2000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2500</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>500</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000001-B9C1-4E6F-8DCF-4F682B3B3FC1}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredBarSeries>
+          </c:ext>
+        </c:extLst>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="2018144127"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2018139967"/>
+        <c:crossesAt val="1000"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="2018139967"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+          <c:max val="2400"/>
+          <c:min val="0"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="#,##0_ " sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2018144127"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+        <c:majorUnit val="400"/>
+      </c:valAx>
+      <c:dTable>
+        <c:showHorzBorder val="1"/>
+        <c:showVertBorder val="1"/>
+        <c:showOutline val="1"/>
+        <c:showKeys val="1"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr rtl="0">
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="ko-KR"/>
+          </a:p>
+        </c:txPr>
+      </c:dTable>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="ko-KR" altLang="en-US"/>
+              <a:t>문구 판매현황</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
               <c:f>정답3!$C$3</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
@@ -3872,7 +4445,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
@@ -4243,7 +4816,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="ko-KR"/>
@@ -4772,6 +5345,46 @@
 </file>
 
 <file path=xl/charts/colors5.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -7346,6 +7959,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
@@ -13302,6 +14418,44 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="차트 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C901C48-44A6-4A79-8725-436925920B5D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -14637,6 +15791,358 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>114694</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>114550</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="그림 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E01EB78B-8E0A-0BB8-65E0-7578CE2C18E8}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7115175" y="2933700"/>
+          <a:ext cx="2819794" cy="1790950"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>609685</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>57480</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{644DA129-EA1B-B40F-75F8-B3D14C6E0B2E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7115175" y="5238750"/>
+          <a:ext cx="609685" cy="2362530"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>219483</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>200404</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5CFDB5DE-A644-CBA6-4DF4-3876A92606FB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9144000" y="5238750"/>
+          <a:ext cx="2924583" cy="2715004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>39</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>190904</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>114784</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="그림 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{819DD6CC-D148-D1C7-7200-5044AD1C8870}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7115175" y="8172450"/>
+          <a:ext cx="2896004" cy="3467584"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>409915</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>133690</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="그림 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C3E83F7F-7145-76EA-A10A-4BA8D9F3B0BC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7115175" y="12153900"/>
+          <a:ext cx="2438740" cy="2438740"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>609968</xdr:colOff>
+      <xdr:row>69</xdr:row>
+      <xdr:rowOff>162269</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="그림 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BBFD1927-AC1D-86BD-371D-EB21CF6DDE92}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9820275" y="12153900"/>
+          <a:ext cx="2638793" cy="2467319"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>48576</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>181146</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="그림 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{231A01D8-152F-6C55-0298-7DB151B32493}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7115175" y="15087600"/>
+          <a:ext cx="6811326" cy="1228896"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>67156</xdr:colOff>
+      <xdr:row>92</xdr:row>
+      <xdr:rowOff>76591</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="그림 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7A1C5F04-84C9-9DC7-F3DB-A366AE3AF93C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7115175" y="16554450"/>
+          <a:ext cx="3448531" cy="2800741"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -17614,9 +19120,6 @@
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="지원자명단"/>
       <sheetName val="사원관리"/>
@@ -17644,9 +19147,6 @@
 <file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <xxl21:alternateUrls>
-      <xxl21:relativeUrl r:id="rId2"/>
-    </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="취득자명단"/>
       <sheetName val="임대관리"/>
@@ -18899,7 +20399,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="B1:G11"/>
+  <dimension ref="B1:M73"/>
   <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="2.625" style="9" customWidth="1"/>
@@ -18908,17 +20408,17 @@
     <col min="8" max="16384" width="8.875" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:7">
+    <row r="1" spans="2:11">
       <c r="B1" s="10" t="s">
         <v>27</v>
       </c>
       <c r="C1" s="10"/>
     </row>
-    <row r="2" spans="2:7">
+    <row r="2" spans="2:11">
       <c r="C2" s="10"/>
       <c r="D2" s="10"/>
     </row>
-    <row r="3" spans="2:7">
+    <row r="3" spans="2:11">
       <c r="B3" s="11" t="s">
         <v>35</v>
       </c>
@@ -18938,7 +20438,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="4" spans="2:7">
+    <row r="4" spans="2:11">
       <c r="B4" s="11" t="s">
         <v>41</v>
       </c>
@@ -18960,7 +20460,7 @@
         <v>2700000</v>
       </c>
     </row>
-    <row r="5" spans="2:7">
+    <row r="5" spans="2:11">
       <c r="B5" s="11" t="s">
         <v>42</v>
       </c>
@@ -18982,7 +20482,7 @@
         <v>400000</v>
       </c>
     </row>
-    <row r="6" spans="2:7">
+    <row r="6" spans="2:11">
       <c r="B6" s="11" t="s">
         <v>43</v>
       </c>
@@ -19004,7 +20504,7 @@
         <v>1116000</v>
       </c>
     </row>
-    <row r="7" spans="2:7">
+    <row r="7" spans="2:11">
       <c r="B7" s="11" t="s">
         <v>44</v>
       </c>
@@ -19026,7 +20526,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="8" spans="2:7">
+    <row r="8" spans="2:11">
       <c r="B8" s="11" t="s">
         <v>45</v>
       </c>
@@ -19048,7 +20548,7 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="9" spans="2:7">
+    <row r="9" spans="2:11">
       <c r="B9" s="11" t="s">
         <v>46</v>
       </c>
@@ -19070,7 +20570,7 @@
         <v>810000</v>
       </c>
     </row>
-    <row r="10" spans="2:7">
+    <row r="10" spans="2:11">
       <c r="B10" s="11" t="s">
         <v>47</v>
       </c>
@@ -19092,7 +20592,7 @@
         <v>800000</v>
       </c>
     </row>
-    <row r="11" spans="2:7">
+    <row r="11" spans="2:11">
       <c r="B11" s="11" t="s">
         <v>48</v>
       </c>
@@ -19112,6 +20612,34 @@
       <c r="G11" s="20">
         <f t="shared" si="1"/>
         <v>260000</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11">
+      <c r="K15" s="9">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="11:13">
+      <c r="K26" s="9">
+        <v>2</v>
+      </c>
+      <c r="M26" s="9" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="40" spans="11:11">
+      <c r="K40" s="9">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="59" spans="11:11">
+      <c r="K59" s="9">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="73" spans="11:11">
+      <c r="K73" s="9">
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/교재/03_차트.xlsx
+++ b/교재/03_차트.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CompUse2nd\교재\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3B483AD1-44DE-4E5B-A6FE-978EACCE4F67}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93D2D9E2-15B0-4E3D-B172-356C7FDB7F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="차트-1" sheetId="6" r:id="rId1"/>
@@ -84,7 +84,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="142" uniqueCount="94">
   <si>
     <t>(단위:천명, %)</t>
     <phoneticPr fontId="4" type="noConversion"/>
@@ -947,6 +947,10 @@
     <t>우클릭-&gt;축서식</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
+  <si>
+    <t>데이터 우클릭-&gt;데이터레이블 서식</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -4831,6 +4835,543 @@
   </mc:AlternateContent>
   <c:chart>
     <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:pieChart>
+        <c:varyColors val="1"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>'차트-4'!$F$3</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>이익금액</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:dPt>
+            <c:idx val="0"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="1"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="2"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="3"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent4"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dPt>
+            <c:idx val="4"/>
+            <c:bubble3D val="0"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent5"/>
+              </a:solidFill>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:dPt>
+          <c:dLbls>
+            <c:spPr>
+              <a:noFill/>
+              <a:ln>
+                <a:noFill/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:txPr>
+              <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                <a:spAutoFit/>
+              </a:bodyPr>
+              <a:lstStyle/>
+              <a:p>
+                <a:pPr>
+                  <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                    <a:solidFill>
+                      <a:schemeClr val="tx1">
+                        <a:lumMod val="75000"/>
+                        <a:lumOff val="25000"/>
+                      </a:schemeClr>
+                    </a:solidFill>
+                    <a:latin typeface="+mn-lt"/>
+                    <a:ea typeface="+mn-ea"/>
+                    <a:cs typeface="+mn-cs"/>
+                  </a:defRPr>
+                </a:pPr>
+                <a:endParaRPr lang="ko-KR"/>
+              </a:p>
+            </c:txPr>
+            <c:dLblPos val="bestFit"/>
+            <c:showLegendKey val="0"/>
+            <c:showVal val="1"/>
+            <c:showCatName val="1"/>
+            <c:showSerName val="0"/>
+            <c:showPercent val="0"/>
+            <c:showBubbleSize val="0"/>
+            <c:showLeaderLines val="1"/>
+            <c:leaderLines>
+              <c:spPr>
+                <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                  <a:solidFill>
+                    <a:schemeClr val="tx1">
+                      <a:lumMod val="35000"/>
+                      <a:lumOff val="65000"/>
+                    </a:schemeClr>
+                  </a:solidFill>
+                  <a:round/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+            </c:leaderLines>
+            <c:extLst>
+              <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+            </c:extLst>
+          </c:dLbls>
+          <c:cat>
+            <c:strRef>
+              <c:f>('차트-4'!$B$4:$B$5,'차트-4'!$B$7:$B$8,'차트-4'!$B$10)</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>액자</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>화분</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>스탠드</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>건조대</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>운동기구</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>('차트-4'!$F$4:$F$5,'차트-4'!$F$7:$F$8,'차트-4'!$F$10)</c:f>
+              <c:numCache>
+                <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>194025</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>105336</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>967950.00000000012</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>680400</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1304100</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-D6DF-4B25-B49E-7764B0748121}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:dLblPos val="bestFit"/>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="1"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+          <c:showLeaderLines val="1"/>
+        </c:dLbls>
+        <c:firstSliceAng val="45"/>
+        <c:extLst>
+          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+            <c15:filteredPieSeries>
+              <c15:ser>
+                <c:idx val="0"/>
+                <c:order val="0"/>
+                <c:tx>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>'차트-4'!$E$3</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="1"/>
+                      <c:pt idx="0">
+                        <c:v>판매금액</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:tx>
+                <c:dPt>
+                  <c:idx val="0"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent1"/>
+                    </a:solidFill>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="1"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent2"/>
+                    </a:solidFill>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="2"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent3"/>
+                    </a:solidFill>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="3"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent4"/>
+                    </a:solidFill>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dPt>
+                  <c:idx val="4"/>
+                  <c:bubble3D val="0"/>
+                  <c:spPr>
+                    <a:solidFill>
+                      <a:schemeClr val="accent5"/>
+                    </a:solidFill>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                </c:dPt>
+                <c:dLbls>
+                  <c:spPr>
+                    <a:noFill/>
+                    <a:ln>
+                      <a:noFill/>
+                    </a:ln>
+                    <a:effectLst/>
+                  </c:spPr>
+                  <c:txPr>
+                    <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" lIns="38100" tIns="19050" rIns="38100" bIns="19050" anchor="ctr" anchorCtr="1">
+                      <a:spAutoFit/>
+                    </a:bodyPr>
+                    <a:lstStyle/>
+                    <a:p>
+                      <a:pPr>
+                        <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                          <a:solidFill>
+                            <a:schemeClr val="tx1">
+                              <a:lumMod val="75000"/>
+                              <a:lumOff val="25000"/>
+                            </a:schemeClr>
+                          </a:solidFill>
+                          <a:latin typeface="+mn-lt"/>
+                          <a:ea typeface="+mn-ea"/>
+                          <a:cs typeface="+mn-cs"/>
+                        </a:defRPr>
+                      </a:pPr>
+                      <a:endParaRPr lang="ko-KR"/>
+                    </a:p>
+                  </c:txPr>
+                  <c:dLblPos val="bestFit"/>
+                  <c:showLegendKey val="0"/>
+                  <c:showVal val="1"/>
+                  <c:showCatName val="0"/>
+                  <c:showSerName val="0"/>
+                  <c:showPercent val="0"/>
+                  <c:showBubbleSize val="0"/>
+                  <c:showLeaderLines val="1"/>
+                  <c:leaderLines>
+                    <c:spPr>
+                      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="35000"/>
+                            <a:lumOff val="65000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:round/>
+                      </a:ln>
+                      <a:effectLst/>
+                    </c:spPr>
+                  </c:leaderLines>
+                  <c:extLst>
+                    <c:ext uri="{CE6537A1-D6FC-4f65-9D91-7224C49458BB}"/>
+                  </c:extLst>
+                </c:dLbls>
+                <c:cat>
+                  <c:strRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>('차트-4'!$B$4:$B$5,'차트-4'!$B$7:$B$8,'차트-4'!$B$10)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:strCache>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>액자</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>화분</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>스탠드</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>건조대</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>운동기구</c:v>
+                      </c:pt>
+                    </c:strCache>
+                  </c:strRef>
+                </c:cat>
+                <c:val>
+                  <c:numRef>
+                    <c:extLst>
+                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
+                        <c15:formulaRef>
+                          <c15:sqref>('차트-4'!$E$4:$E$5,'차트-4'!$E$7:$E$8,'차트-4'!$E$10)</c15:sqref>
+                        </c15:formulaRef>
+                      </c:ext>
+                    </c:extLst>
+                    <c:numCache>
+                      <c:formatCode>_(* #,##0_);_(* \(#,##0\);_(* "-"_);_(@_)</c:formatCode>
+                      <c:ptCount val="5"/>
+                      <c:pt idx="0">
+                        <c:v>1293500</c:v>
+                      </c:pt>
+                      <c:pt idx="1">
+                        <c:v>501600</c:v>
+                      </c:pt>
+                      <c:pt idx="2">
+                        <c:v>3585000</c:v>
+                      </c:pt>
+                      <c:pt idx="3">
+                        <c:v>2520000</c:v>
+                      </c:pt>
+                      <c:pt idx="4">
+                        <c:v>5670000</c:v>
+                      </c:pt>
+                    </c:numCache>
+                  </c:numRef>
+                </c:val>
+                <c:extLst>
+                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+                    <c16:uniqueId val="{00000000-D6DF-4B25-B49E-7764B0748121}"/>
+                  </c:ext>
+                </c:extLst>
+              </c15:ser>
+            </c15:filteredPieSeries>
+          </c:ext>
+        </c:extLst>
+      </c:pieChart>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="ko-KR"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="ko-KR"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart9.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="ko-KR"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
       <c:tx>
         <c:rich>
           <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
@@ -5385,6 +5926,46 @@
 </file>
 
 <file path=xl/charts/colors6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -8462,6 +9043,509 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/ctrlProps/ctrlProp1.xml><?xml version="1.0" encoding="utf-8"?>
 <formControlPr xmlns="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" objectType="Button" lockText="1"/>
 </file>
@@ -17502,6 +18586,44 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>52</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="8" name="차트 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A3605655-69B8-4B67-B4DA-56D3026995FE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -19114,6 +20236,358 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:oneCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>381425</xdr:colOff>
+      <xdr:row>24</xdr:row>
+      <xdr:rowOff>57392</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="6" name="그림 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AB09B233-D580-77FE-B64D-40B5C0C86968}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7581900" y="3352800"/>
+          <a:ext cx="3048425" cy="1733792"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>229656</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>38632</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="그림 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{56A9F191-41A9-BC78-3062-4966470962DE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7581900" y="5657850"/>
+          <a:ext cx="7563906" cy="3810532"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>190992</xdr:colOff>
+      <xdr:row>54</xdr:row>
+      <xdr:rowOff>57333</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="그림 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6C85036C-096D-F9E8-BD75-F74CC0B68D05}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7581900" y="10058400"/>
+          <a:ext cx="3524742" cy="1314633"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>57</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>324826</xdr:colOff>
+      <xdr:row>75</xdr:row>
+      <xdr:rowOff>162474</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="그림 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{44E73F8E-BFE7-CA34-013F-0AD2F04BDAE0}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7581900" y="11944350"/>
+          <a:ext cx="6992326" cy="3934374"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>77</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>200518</xdr:colOff>
+      <xdr:row>87</xdr:row>
+      <xdr:rowOff>124135</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="그림 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{795D524A-43F3-E42A-D617-5D63729320FF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7581900" y="16135350"/>
+          <a:ext cx="3534268" cy="2219635"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>104775</xdr:colOff>
+      <xdr:row>90</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>9884</xdr:colOff>
+      <xdr:row>103</xdr:row>
+      <xdr:rowOff>57529</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="그림 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B7BC0D3A-4CCC-512A-8AFD-A14A119D4708}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7686675" y="18926175"/>
+          <a:ext cx="2572109" cy="2715004"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>11</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>267203</xdr:colOff>
+      <xdr:row>123</xdr:row>
+      <xdr:rowOff>38573</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="14" name="그림 13">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{FEF7EC31-2AB3-4D0C-F84D-8226BC19CFD1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7581900" y="22421850"/>
+          <a:ext cx="3600953" cy="3391373"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>107</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>48004</xdr:colOff>
+      <xdr:row>122</xdr:row>
+      <xdr:rowOff>76649</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="그림 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{97CA3DEA-A07A-EFA5-4A7E-DCDAB07381CC}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="11582400" y="22421850"/>
+          <a:ext cx="2715004" cy="3219899"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -21261,7 +22735,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="B1:F10"/>
+  <dimension ref="B1:L108"/>
   <sheetFormatPr defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="2.625" style="16" customWidth="1"/>
@@ -21802,6 +23276,36 @@
         <v>1304100</v>
       </c>
     </row>
+    <row r="17" spans="11:11">
+      <c r="K17" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="11:11">
+      <c r="K28" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="11:11">
+      <c r="K49" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="58" spans="11:11">
+      <c r="K58" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="90" spans="12:12">
+      <c r="L90" s="16" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="108" spans="11:11">
+      <c r="K108" s="16">
+        <v>5</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <printOptions headings="1" gridLines="1"/>
